--- a/docs/print-proof/print-proof-timetable.xlsx
+++ b/docs/print-proof/print-proof-timetable.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,25 +427,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>الأحد</v>
+        <v>الاثنين</v>
       </c>
       <c r="B2" t="str">
         <v>08:00 - 10:00</v>
       </c>
       <c r="C2" t="str">
-        <v>FX-C101</v>
+        <v>FX-C126</v>
       </c>
       <c r="D2" t="str">
-        <v>مقدمة في علوم الحاسوب</v>
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
       </c>
       <c r="E2" t="str">
-        <v>عملي</v>
+        <v>نظري</v>
       </c>
       <c r="F2" t="str">
-        <v>د. عبد الرحمن الشرعبي</v>
+        <v>د. سارة أحمد المقطري</v>
       </c>
       <c r="G2" t="str">
-        <v>LAB-1 مختبر الحاسوب الأول</v>
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -456,30 +456,3098 @@
         <v>الاثنين</v>
       </c>
       <c r="B3" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C3" t="str">
+        <v>FX-C102</v>
+      </c>
+      <c r="D3" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E3" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F3" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G3" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B4" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C4" t="str">
+        <v>FX-C108</v>
+      </c>
+      <c r="D4" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E4" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F4" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G4" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B5" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C5" t="str">
+        <v>FX-C114</v>
+      </c>
+      <c r="D5" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E5" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F5" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G5" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B6" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C6" t="str">
+        <v>FX-C120</v>
+      </c>
+      <c r="D6" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E6" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F6" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G6" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B7" t="str">
         <v>08:00 - 10:00</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C7" t="str">
+        <v>FX-C116</v>
+      </c>
+      <c r="D7" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E7" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F7" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G7" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B8" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C8" t="str">
+        <v>FX-C122</v>
+      </c>
+      <c r="D8" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E8" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F8" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G8" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B9" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C9" t="str">
+        <v>FX-C128</v>
+      </c>
+      <c r="D9" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E9" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F9" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G9" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B10" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C10" t="str">
+        <v>FX-C104</v>
+      </c>
+      <c r="D10" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E10" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F10" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G10" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B11" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C11" t="str">
+        <v>FX-C110</v>
+      </c>
+      <c r="D11" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E11" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F11" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G11" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B12" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C12" t="str">
+        <v>FX-C106</v>
+      </c>
+      <c r="D12" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E12" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F12" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G12" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B13" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C13" t="str">
+        <v>FX-C112</v>
+      </c>
+      <c r="D13" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E13" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F13" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G13" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B14" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C14" t="str">
+        <v>FX-C118</v>
+      </c>
+      <c r="D14" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E14" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F14" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G14" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B15" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C15" t="str">
+        <v>FX-C124</v>
+      </c>
+      <c r="D15" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E15" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F15" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G15" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B16" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C16" t="str">
+        <v>FX-C130</v>
+      </c>
+      <c r="D16" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E16" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F16" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G16" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B17" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C17" t="str">
         <v>FX-C101</v>
       </c>
-      <c r="D3" t="str">
-        <v>مقدمة في علوم الحاسوب</v>
-      </c>
-      <c r="E3" t="str">
-        <v>نظري</v>
-      </c>
-      <c r="F3" t="str">
-        <v>د. عبد الرحمن الشرعبي</v>
-      </c>
-      <c r="G3" t="str">
-        <v>H-201 قاعة المحاضرات ٢٠١</v>
-      </c>
-      <c r="H3" t="str">
+      <c r="D17" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E17" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F17" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G17" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B18" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C18" t="str">
+        <v>FX-C107</v>
+      </c>
+      <c r="D18" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E18" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F18" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G18" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B19" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C19" t="str">
+        <v>FX-C113</v>
+      </c>
+      <c r="D19" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E19" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F19" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G19" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B20" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C20" t="str">
+        <v>FX-C119</v>
+      </c>
+      <c r="D20" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E20" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F20" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G20" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B21" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C21" t="str">
+        <v>FX-C125</v>
+      </c>
+      <c r="D21" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E21" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F21" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G21" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B22" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C22" t="str">
+        <v>FX-C121</v>
+      </c>
+      <c r="D22" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E22" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F22" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G22" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B23" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C23" t="str">
+        <v>FX-C127</v>
+      </c>
+      <c r="D23" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E23" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F23" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G23" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B24" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C24" t="str">
+        <v>FX-C103</v>
+      </c>
+      <c r="D24" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E24" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F24" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G24" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B25" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C25" t="str">
+        <v>FX-C109</v>
+      </c>
+      <c r="D25" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E25" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F25" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G25" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B26" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C26" t="str">
+        <v>FX-C115</v>
+      </c>
+      <c r="D26" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E26" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F26" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G26" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B27" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C27" t="str">
+        <v>FX-C111</v>
+      </c>
+      <c r="D27" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E27" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F27" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G27" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B28" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C28" t="str">
+        <v>FX-C117</v>
+      </c>
+      <c r="D28" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E28" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F28" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G28" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B29" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C29" t="str">
+        <v>FX-C123</v>
+      </c>
+      <c r="D29" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E29" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F29" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G29" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B30" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C30" t="str">
+        <v>FX-C129</v>
+      </c>
+      <c r="D30" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E30" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F30" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G30" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B31" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C31" t="str">
+        <v>FX-C105</v>
+      </c>
+      <c r="D31" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E31" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F31" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G31" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B32" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C32" t="str">
+        <v>FX-C226</v>
+      </c>
+      <c r="D32" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E32" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F32" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G32" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B33" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C33" t="str">
+        <v>FX-C202</v>
+      </c>
+      <c r="D33" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E33" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F33" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G33" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B34" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C34" t="str">
+        <v>FX-C208</v>
+      </c>
+      <c r="D34" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E34" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F34" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G34" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B35" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C35" t="str">
+        <v>FX-C214</v>
+      </c>
+      <c r="D35" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E35" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F35" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G35" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B36" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C36" t="str">
+        <v>FX-C220</v>
+      </c>
+      <c r="D36" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E36" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F36" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G36" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B37" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C37" t="str">
+        <v>FX-C216</v>
+      </c>
+      <c r="D37" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E37" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F37" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G37" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B38" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C38" t="str">
+        <v>FX-C222</v>
+      </c>
+      <c r="D38" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E38" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F38" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G38" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B39" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C39" t="str">
+        <v>FX-C228</v>
+      </c>
+      <c r="D39" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E39" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F39" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G39" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B40" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C40" t="str">
+        <v>FX-C204</v>
+      </c>
+      <c r="D40" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E40" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F40" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G40" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B41" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C41" t="str">
+        <v>FX-C210</v>
+      </c>
+      <c r="D41" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E41" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F41" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G41" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B42" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C42" t="str">
+        <v>FX-C206</v>
+      </c>
+      <c r="D42" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E42" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F42" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G42" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B43" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C43" t="str">
+        <v>FX-C212</v>
+      </c>
+      <c r="D43" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E43" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F43" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G43" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B44" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C44" t="str">
+        <v>FX-C218</v>
+      </c>
+      <c r="D44" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E44" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F44" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G44" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B45" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C45" t="str">
+        <v>FX-C224</v>
+      </c>
+      <c r="D45" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E45" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F45" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G45" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B46" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C46" t="str">
+        <v>FX-C230</v>
+      </c>
+      <c r="D46" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E46" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F46" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G46" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B47" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C47" t="str">
+        <v>FX-C201</v>
+      </c>
+      <c r="D47" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E47" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F47" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G47" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B48" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C48" t="str">
+        <v>FX-C207</v>
+      </c>
+      <c r="D48" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E48" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F48" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G48" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B49" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C49" t="str">
+        <v>FX-C213</v>
+      </c>
+      <c r="D49" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E49" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F49" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G49" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B50" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C50" t="str">
+        <v>FX-C219</v>
+      </c>
+      <c r="D50" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E50" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F50" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G50" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B51" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C51" t="str">
+        <v>FX-C225</v>
+      </c>
+      <c r="D51" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E51" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F51" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G51" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B52" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C52" t="str">
+        <v>FX-C221</v>
+      </c>
+      <c r="D52" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E52" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F52" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G52" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B53" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C53" t="str">
+        <v>FX-C227</v>
+      </c>
+      <c r="D53" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E53" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F53" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G53" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B54" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C54" t="str">
+        <v>FX-C203</v>
+      </c>
+      <c r="D54" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E54" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F54" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G54" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B55" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C55" t="str">
+        <v>FX-C209</v>
+      </c>
+      <c r="D55" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E55" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F55" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G55" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B56" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C56" t="str">
+        <v>FX-C215</v>
+      </c>
+      <c r="D56" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E56" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F56" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G56" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B57" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C57" t="str">
+        <v>FX-C211</v>
+      </c>
+      <c r="D57" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E57" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F57" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G57" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B58" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C58" t="str">
+        <v>FX-C217</v>
+      </c>
+      <c r="D58" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E58" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F58" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G58" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B59" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C59" t="str">
+        <v>FX-C223</v>
+      </c>
+      <c r="D59" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E59" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F59" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G59" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B60" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C60" t="str">
+        <v>FX-C229</v>
+      </c>
+      <c r="D60" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E60" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F60" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G60" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B61" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C61" t="str">
+        <v>FX-C205</v>
+      </c>
+      <c r="D61" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E61" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F61" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G61" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B62" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C62" t="str">
+        <v>FX-C326</v>
+      </c>
+      <c r="D62" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E62" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F62" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G62" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B63" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C63" t="str">
+        <v>FX-C302</v>
+      </c>
+      <c r="D63" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E63" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F63" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G63" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B64" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C64" t="str">
+        <v>FX-C308</v>
+      </c>
+      <c r="D64" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E64" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F64" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G64" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B65" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C65" t="str">
+        <v>FX-C314</v>
+      </c>
+      <c r="D65" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E65" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F65" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G65" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B66" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C66" t="str">
+        <v>FX-C320</v>
+      </c>
+      <c r="D66" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E66" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F66" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G66" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B67" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C67" t="str">
+        <v>FX-C316</v>
+      </c>
+      <c r="D67" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E67" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F67" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G67" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B68" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C68" t="str">
+        <v>FX-C322</v>
+      </c>
+      <c r="D68" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E68" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F68" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G68" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B69" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C69" t="str">
+        <v>FX-C328</v>
+      </c>
+      <c r="D69" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E69" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F69" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G69" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B70" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C70" t="str">
+        <v>FX-C304</v>
+      </c>
+      <c r="D70" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E70" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F70" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G70" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B71" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C71" t="str">
+        <v>FX-C310</v>
+      </c>
+      <c r="D71" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E71" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F71" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G71" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B72" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C72" t="str">
+        <v>FX-C306</v>
+      </c>
+      <c r="D72" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E72" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F72" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G72" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B73" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C73" t="str">
+        <v>FX-C312</v>
+      </c>
+      <c r="D73" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E73" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F73" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G73" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B74" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C74" t="str">
+        <v>FX-C318</v>
+      </c>
+      <c r="D74" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E74" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F74" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G74" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B75" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C75" t="str">
+        <v>FX-C324</v>
+      </c>
+      <c r="D75" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E75" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F75" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G75" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B76" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C76" t="str">
+        <v>FX-C330</v>
+      </c>
+      <c r="D76" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E76" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F76" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G76" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B77" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C77" t="str">
+        <v>FX-C301</v>
+      </c>
+      <c r="D77" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E77" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F77" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G77" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B78" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C78" t="str">
+        <v>FX-C307</v>
+      </c>
+      <c r="D78" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E78" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F78" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G78" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B79" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C79" t="str">
+        <v>FX-C313</v>
+      </c>
+      <c r="D79" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E79" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F79" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G79" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B80" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C80" t="str">
+        <v>FX-C319</v>
+      </c>
+      <c r="D80" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E80" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F80" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G80" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B81" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C81" t="str">
+        <v>FX-C325</v>
+      </c>
+      <c r="D81" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E81" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F81" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G81" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B82" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C82" t="str">
+        <v>FX-C321</v>
+      </c>
+      <c r="D82" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E82" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F82" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G82" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B83" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C83" t="str">
+        <v>FX-C327</v>
+      </c>
+      <c r="D83" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E83" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F83" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G83" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B84" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C84" t="str">
+        <v>FX-C303</v>
+      </c>
+      <c r="D84" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E84" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F84" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G84" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B85" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C85" t="str">
+        <v>FX-C309</v>
+      </c>
+      <c r="D85" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E85" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F85" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G85" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B86" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C86" t="str">
+        <v>FX-C315</v>
+      </c>
+      <c r="D86" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E86" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F86" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G86" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B87" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C87" t="str">
+        <v>FX-C311</v>
+      </c>
+      <c r="D87" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E87" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F87" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G87" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B88" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C88" t="str">
+        <v>FX-C317</v>
+      </c>
+      <c r="D88" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E88" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F88" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G88" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B89" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C89" t="str">
+        <v>FX-C323</v>
+      </c>
+      <c r="D89" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E89" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F89" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G89" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B90" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C90" t="str">
+        <v>FX-C329</v>
+      </c>
+      <c r="D90" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E90" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F90" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G90" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B91" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C91" t="str">
+        <v>FX-C305</v>
+      </c>
+      <c r="D91" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E91" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F91" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G91" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B92" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C92" t="str">
+        <v>FX-C426</v>
+      </c>
+      <c r="D92" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E92" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F92" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G92" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B93" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C93" t="str">
+        <v>FX-C402</v>
+      </c>
+      <c r="D93" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E93" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F93" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G93" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B94" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C94" t="str">
+        <v>FX-C408</v>
+      </c>
+      <c r="D94" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E94" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F94" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G94" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B95" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C95" t="str">
+        <v>FX-C414</v>
+      </c>
+      <c r="D95" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E95" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F95" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G95" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>الاثنين</v>
+      </c>
+      <c r="B96" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C96" t="str">
+        <v>FX-C420</v>
+      </c>
+      <c r="D96" t="str">
+        <v>قواعد البيانات الموزّعة وتحسين الاستعلامات</v>
+      </c>
+      <c r="E96" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F96" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G96" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B97" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C97" t="str">
+        <v>FX-C416</v>
+      </c>
+      <c r="D97" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E97" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F97" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G97" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B98" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C98" t="str">
+        <v>FX-C422</v>
+      </c>
+      <c r="D98" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E98" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F98" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G98" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B99" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C99" t="str">
+        <v>FX-C428</v>
+      </c>
+      <c r="D99" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E99" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F99" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G99" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B100" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C100" t="str">
+        <v>FX-C404</v>
+      </c>
+      <c r="D100" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E100" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F100" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G100" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>الأربعاء</v>
+      </c>
+      <c r="B101" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C101" t="str">
+        <v>FX-C410</v>
+      </c>
+      <c r="D101" t="str">
+        <v>الذكاء الاصطناعي وتعلّم الآلة التطبيقي</v>
+      </c>
+      <c r="E101" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F101" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G101" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B102" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C102" t="str">
+        <v>FX-C406</v>
+      </c>
+      <c r="D102" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E102" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F102" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G102" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B103" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C103" t="str">
+        <v>FX-C412</v>
+      </c>
+      <c r="D103" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E103" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F103" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G103" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B104" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C104" t="str">
+        <v>FX-C418</v>
+      </c>
+      <c r="D104" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E104" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F104" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G104" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B105" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C105" t="str">
+        <v>FX-C424</v>
+      </c>
+      <c r="D105" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E105" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F105" t="str">
+        <v>د. سارة أحمد المقطري</v>
+      </c>
+      <c r="G105" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>الجمعة</v>
+      </c>
+      <c r="B106" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C106" t="str">
+        <v>FX-C430</v>
+      </c>
+      <c r="D106" t="str">
+        <v>هندسة المتطلّبات وإدارة مشاريع تقنية المعلومات</v>
+      </c>
+      <c r="E106" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F106" t="str">
+        <v>أ. فاطمة صالح العريقي</v>
+      </c>
+      <c r="G106" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B107" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C107" t="str">
+        <v>FX-C401</v>
+      </c>
+      <c r="D107" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E107" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F107" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G107" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B108" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C108" t="str">
+        <v>FX-C407</v>
+      </c>
+      <c r="D108" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E108" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F108" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G108" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B109" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C109" t="str">
+        <v>FX-C413</v>
+      </c>
+      <c r="D109" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E109" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F109" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G109" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B110" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C110" t="str">
+        <v>FX-C419</v>
+      </c>
+      <c r="D110" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E110" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F110" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G110" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>الأحد</v>
+      </c>
+      <c r="B111" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C111" t="str">
+        <v>FX-C425</v>
+      </c>
+      <c r="D111" t="str">
+        <v>أساسيات هندسة البرمجيات وتحليل النظم المتقدمة</v>
+      </c>
+      <c r="E111" t="str">
+        <v>عملي</v>
+      </c>
+      <c r="F111" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G111" t="str">
+        <v>H-101 قاعة المحاضرات الكبرى رقم ١٠١</v>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B112" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C112" t="str">
+        <v>FX-C421</v>
+      </c>
+      <c r="D112" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E112" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F112" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G112" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B113" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C113" t="str">
+        <v>FX-C427</v>
+      </c>
+      <c r="D113" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E113" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F113" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G113" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B114" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C114" t="str">
+        <v>FX-C403</v>
+      </c>
+      <c r="D114" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E114" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F114" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G114" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B115" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C115" t="str">
+        <v>FX-C409</v>
+      </c>
+      <c r="D115" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E115" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F115" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G115" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>الثلاثاء</v>
+      </c>
+      <c r="B116" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C116" t="str">
+        <v>FX-C415</v>
+      </c>
+      <c r="D116" t="str">
+        <v>شبكات الحاسوب وبروتوكولات الاتصال الحديثة</v>
+      </c>
+      <c r="E116" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F116" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G116" t="str">
+        <v>H-305 قاعة الدراسات العليا ٣٠٥</v>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B117" t="str">
+        <v>08:00 - 10:00</v>
+      </c>
+      <c r="C117" t="str">
+        <v>FX-C411</v>
+      </c>
+      <c r="D117" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E117" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F117" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G117" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B118" t="str">
+        <v>10:00 - 12:00</v>
+      </c>
+      <c r="C118" t="str">
+        <v>FX-C417</v>
+      </c>
+      <c r="D118" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E118" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F118" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G118" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B119" t="str">
+        <v>12:00 - 14:00</v>
+      </c>
+      <c r="C119" t="str">
+        <v>FX-C423</v>
+      </c>
+      <c r="D119" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E119" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F119" t="str">
+        <v>أ.د. محمد عبدالله الحكيمي</v>
+      </c>
+      <c r="G119" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B120" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="C120" t="str">
+        <v>FX-C429</v>
+      </c>
+      <c r="D120" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E120" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F120" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G120" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>الخميس</v>
+      </c>
+      <c r="B121" t="str">
+        <v>16:00 - 18:00</v>
+      </c>
+      <c r="C121" t="str">
+        <v>FX-C405</v>
+      </c>
+      <c r="D121" t="str">
+        <v>أمن المعلومات والتشفير وحماية البنية التحتية الرقمية</v>
+      </c>
+      <c r="E121" t="str">
+        <v>نظري</v>
+      </c>
+      <c r="F121" t="str">
+        <v>د. عبدالسلام ناجي الشميري</v>
+      </c>
+      <c r="G121" t="str">
+        <v>LAB-3 مختبر الشبكات والأنظمة الموزّعة</v>
+      </c>
+      <c r="H121" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H121"/>
   </ignoredErrors>
 </worksheet>
 </file>